--- a/5_figures/data/A_Tableau_SNV_Transplanted.xlsx
+++ b/5_figures/data/A_Tableau_SNV_Transplanted.xlsx
@@ -22,28 +22,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="79">
   <si>
-    <t xml:space="preserve">flfl_MPNST_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flfl_MPNST_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flfl_MPNST_E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flfl_MPNST_F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_flfl_MPNST_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_flfl_MPNST_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_flfl_MPNST_E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_flfl_MPNST_F</t>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M’</t>
   </si>
   <si>
     <t xml:space="preserve">Tumor Type</t>
@@ -1354,7 +1354,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A3:X58"/>
-  <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.51171875" defaultRowHeight="16" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.33"/>
@@ -1372,7 +1372,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="73" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
         <v>0</v>
